--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/5483-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/5483-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ADD7B985-548A-45CF-8881-5CEF35AAA913}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4B5C985C-CEA7-4C27-AF84-5902BECC0140}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{7A25F10D-AF18-4D29-B1ED-A595BA0C6DDD}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{BBDFBDE3-372B-4BF9-AF17-6A5E3C74C6F5}"/>
   </bookViews>
   <sheets>
     <sheet name="5483-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1537,23 +1537,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{776A25B8-539D-4079-8ADF-550F40C2BD58}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9912B582-58D4-4DEB-8F5D-5A9F456AA9B1}">
   <dimension ref="A1:R46"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="7" width="8.33203125" customWidth="1"/>
-    <col min="8" max="8" width="8" customWidth="1"/>
-    <col min="9" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.5546875" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="7" width="10.5" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="18" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
@@ -1581,7 +1580,7 @@
       <c r="Q1" s="33"/>
       <c r="R1" s="25"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="26" t="s">
         <v>1</v>
       </c>
@@ -1611,7 +1610,7 @@
       <c r="Q2" s="35"/>
       <c r="R2" s="36"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="26" t="s">
         <v>2</v>
       </c>
@@ -1657,7 +1656,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="28"/>
       <c r="B4" s="29"/>
       <c r="C4" s="7"/>
@@ -1707,7 +1706,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="40">
         <v>2026</v>
       </c>
@@ -1761,7 +1760,7 @@
         <v>1.61</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="42"/>
       <c r="B6" s="43"/>
       <c r="C6" s="45"/>
@@ -1787,7 +1786,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>27</v>
       </c>
@@ -1843,7 +1842,7 @@
         <v>0.81</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="50">
         <v>2025</v>
       </c>
@@ -1897,7 +1896,7 @@
         <v>5.65</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
         <v>27</v>
       </c>
@@ -1953,7 +1952,7 @@
         <v>3.17</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>27</v>
       </c>
@@ -2009,7 +2008,7 @@
         <v>2.48</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="52">
         <v>2024</v>
       </c>
@@ -2063,7 +2062,7 @@
         <v>4.18</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>27</v>
       </c>
@@ -2119,7 +2118,7 @@
         <v>2.46</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>27</v>
       </c>
@@ -2175,7 +2174,7 @@
         <v>1.72</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="50">
         <v>2023</v>
       </c>
@@ -2229,7 +2228,7 @@
         <v>5.19</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
         <v>27</v>
       </c>
@@ -2285,7 +2284,7 @@
         <v>3.21</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
         <v>27</v>
       </c>
@@ -2341,7 +2340,7 @@
         <v>1.98</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="52">
         <v>2022</v>
       </c>
@@ -2395,7 +2394,7 @@
         <v>4.63</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>27</v>
       </c>
@@ -2451,7 +2450,7 @@
         <v>3.11</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>27</v>
       </c>
@@ -2507,7 +2506,7 @@
         <v>1.52</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="50">
         <v>2021</v>
       </c>
@@ -2561,7 +2560,7 @@
         <v>4.63</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
         <v>27</v>
       </c>
@@ -2617,7 +2616,7 @@
         <v>2.58</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="19" t="s">
         <v>27</v>
       </c>
@@ -2673,7 +2672,7 @@
         <v>2.0499999999999998</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="52">
         <v>2020</v>
       </c>
@@ -2727,7 +2726,7 @@
         <v>4.63</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="50">
         <v>2019</v>
       </c>
@@ -2781,7 +2780,7 @@
         <v>3.41</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="52">
         <v>2018</v>
       </c>
@@ -2835,7 +2834,7 @@
         <v>2.61</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="50">
         <v>2017</v>
       </c>
@@ -2889,7 +2888,7 @@
         <v>2.94</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="52">
         <v>2016</v>
       </c>
@@ -2943,7 +2942,7 @@
         <v>4.0599999999999996</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="50">
         <v>2015</v>
       </c>
@@ -2997,7 +2996,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="52">
         <v>2014</v>
       </c>
@@ -3051,7 +3050,7 @@
         <v>1.82</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="50">
         <v>2013</v>
       </c>
@@ -3105,7 +3104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="52">
         <v>2012</v>
       </c>
@@ -3159,7 +3158,7 @@
         <v>2.59</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="50">
         <v>2011</v>
       </c>
@@ -3213,7 +3212,7 @@
         <v>6.71</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="52">
         <v>2010</v>
       </c>
@@ -3267,7 +3266,7 @@
         <v>2.21</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="50">
         <v>2009</v>
       </c>
@@ -3321,7 +3320,7 @@
         <v>5.0199999999999996</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="52">
         <v>2008</v>
       </c>
@@ -3375,7 +3374,7 @@
         <v>4.57</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="50">
         <v>2007</v>
       </c>
@@ -3429,7 +3428,7 @@
         <v>1.24</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="52">
         <v>2006</v>
       </c>
@@ -3483,7 +3482,7 @@
         <v>1.61</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="50">
         <v>2005</v>
       </c>
@@ -3537,7 +3536,7 @@
         <v>1.93</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="52">
         <v>2004</v>
       </c>
@@ -3591,7 +3590,7 @@
         <v>4.88</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="50">
         <v>2003</v>
       </c>
@@ -3645,7 +3644,7 @@
         <v>2.65</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="52">
         <v>2002</v>
       </c>
@@ -3699,7 +3698,7 @@
         <v>3.74</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="50">
         <v>2001</v>
       </c>
@@ -3753,7 +3752,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="52">
         <v>2000</v>
       </c>
@@ -3807,7 +3806,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="50">
         <v>1999</v>
       </c>
@@ -3861,7 +3860,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="52">
         <v>1998</v>
       </c>
@@ -3915,7 +3914,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="50" t="s">
         <v>49</v>
       </c>
